--- a/data/2024-25/ICEHLdelegacije.xlsx
+++ b/data/2024-25/ICEHLdelegacije.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EF36B3-6B43-4247-BD48-DA74CCB2E2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="ICEHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="ICEHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet name="ICEHL" sheetId="1" r:id="rId1"/>
+    <sheet name="ICEHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="ICEHL_DAT_STRING" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="516">
   <si>
     <t>SmetanaLa</t>
   </si>
@@ -433,9 +447,6 @@
   </si>
   <si>
     <t>2025-03-04</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
   </si>
   <si>
     <t>2025-03-07</t>
@@ -1572,14 +1583,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1883,9 +1894,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AZ134"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1942,34 +1953,34 @@
     <col min="53" max="53" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.45" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>COUNTIF(A4:A97,"&lt;&gt;")</f>
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B2">
         <f>COUNTIF(B4:B95,"&lt;&gt;")</f>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(C4:C94,"&lt;&gt;")</f>
-        <v>49</v>
+        <f>COUNTIF(C4:C92,"&lt;&gt;")</f>
+        <v>62</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(D4:D94,"&lt;&gt;")</f>
-        <v>45</v>
+        <f>COUNTIF(D4:D91,"&lt;&gt;")</f>
+        <v>58</v>
       </c>
       <c r="E2">
         <f>COUNTIF(E4:E98,"&lt;&gt;")</f>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F2">
         <f>COUNTIF(F4:F100,"&lt;&gt;")</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <f>COUNTIF(G4:G100,"&lt;&gt;")</f>
-        <v>38</v>
+        <f>COUNTIF(G4:G99,"&lt;&gt;")</f>
+        <v>48</v>
       </c>
       <c r="H2">
         <f>COUNTIF(H4:H99,"&lt;&gt;")</f>
@@ -1977,19 +1988,19 @@
       </c>
       <c r="I2">
         <f>COUNTIF(I4:I99,"&lt;&gt;")</f>
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J2">
         <f>COUNTIF(J4:J97,"&lt;&gt;")</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K2">
         <f>COUNTIF(K4:K97,"&lt;&gt;")</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L2">
         <f>COUNTIF(L4:L98,"&lt;&gt;")</f>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M2">
         <f>COUNTIF(M4:M97,"&lt;&gt;")</f>
@@ -1997,11 +2008,11 @@
       </c>
       <c r="N2">
         <f>COUNTIF(N4:N98,"&lt;&gt;")</f>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O2">
-        <f>COUNTIF(O4:O99,"&lt;&gt;")</f>
-        <v>32</v>
+        <f>COUNTIF(O4:O98,"&lt;&gt;")</f>
+        <v>42</v>
       </c>
       <c r="P2">
         <f>COUNTIF(P4:P100,"&lt;&gt;")</f>
@@ -2009,11 +2020,11 @@
       </c>
       <c r="Q2">
         <f>COUNTIF(Q4:Q100,"&lt;&gt;")</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R2">
-        <f>COUNTIF(R4:R98,"&lt;&gt;")</f>
-        <v>32</v>
+        <f>COUNTIF(R4:R97,"&lt;&gt;")</f>
+        <v>41</v>
       </c>
       <c r="S2">
         <f>COUNTIF(S4:S100,"&lt;&gt;")</f>
@@ -2025,7 +2036,7 @@
       </c>
       <c r="U2">
         <f>COUNTIF(U4:U99,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="V2">
         <f>COUNTIF(V4:V95,"&lt;&gt;")</f>
@@ -2033,7 +2044,7 @@
       </c>
       <c r="W2">
         <f>COUNTIF(W4:W100,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X2">
         <f>COUNTIF(X4:X99,"&lt;&gt;")</f>
@@ -2045,19 +2056,19 @@
       </c>
       <c r="Z2">
         <f>COUNTIF(Z4:Z96,"&lt;&gt;")</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA2">
         <f>COUNTIF(AA4:AA100,"&lt;&gt;")</f>
         <v>27</v>
       </c>
       <c r="AB2">
-        <f>COUNTIF(AB4:AB92,"&lt;&gt;")</f>
-        <v>25</v>
+        <f>COUNTIF(AB4:AB91,"&lt;&gt;")</f>
+        <v>36</v>
       </c>
       <c r="AC2">
         <f>COUNTIF(AC4:AC97,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AD2">
         <f>COUNTIF(AD4:AD100,"&lt;&gt;")</f>
@@ -2073,11 +2084,11 @@
       </c>
       <c r="AG2">
         <f>COUNTIF(AG4:AG87,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="AH2">
-        <f>COUNTIF(AH4:AH94,"&lt;&gt;")</f>
-        <v>22</v>
+        <f>COUNTIF(AH4:AH93,"&lt;&gt;")</f>
+        <v>29</v>
       </c>
       <c r="AI2">
         <f>COUNTIF(AI4:AI97,"&lt;&gt;")</f>
@@ -2113,7 +2124,7 @@
       </c>
       <c r="AQ2">
         <f>COUNTIF(AQ4:AQ98,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR2">
         <f>COUNTIF(AR4:AR100,"&lt;&gt;")</f>
@@ -2152,7 +2163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2310,7 +2321,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -2468,7 +2479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -2614,7 +2625,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -2754,7 +2765,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -2894,7 +2905,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3031,7 +3042,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -3168,7 +3179,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -3302,7 +3313,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3433,7 +3444,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -3564,7 +3575,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -3692,7 +3703,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -3820,7 +3831,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -3948,7 +3959,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -4070,7 +4081,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -4189,7 +4200,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -4308,7 +4319,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>83</v>
       </c>
@@ -4427,7 +4438,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -4543,7 +4554,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -4659,7 +4670,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4766,7 +4777,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -4873,7 +4884,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -4977,7 +4988,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -5081,7 +5092,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -5280,7 +5291,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>100</v>
       </c>
@@ -5375,7 +5386,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -5467,10 +5478,10 @@
         <v>138</v>
       </c>
       <c r="AH29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>108</v>
       </c>
@@ -5559,13 +5570,13 @@
         <v>138</v>
       </c>
       <c r="AG30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AH30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -5642,19 +5653,19 @@
         <v>133</v>
       </c>
       <c r="AB31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AC31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG31" t="s">
         <v>136</v>
       </c>
       <c r="AH31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -5728,19 +5739,19 @@
         <v>138</v>
       </c>
       <c r="AB32" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>143</v>
+      </c>
+      <c r="AG32" t="s">
         <v>144</v>
       </c>
-      <c r="AC32" t="s">
-        <v>144</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>145</v>
-      </c>
       <c r="AH32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5814,19 +5825,16 @@
         <v>136</v>
       </c>
       <c r="AB33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AC33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG33" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -5891,16 +5899,16 @@
         <v>138</v>
       </c>
       <c r="AB34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -5944,7 +5952,7 @@
         <v>109</v>
       </c>
       <c r="O35" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="P35" t="s">
         <v>109</v>
@@ -5962,16 +5970,16 @@
         <v>136</v>
       </c>
       <c r="AB35" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AC35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -6012,7 +6020,7 @@
         <v>130</v>
       </c>
       <c r="O36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q36" t="s">
         <v>138</v>
@@ -6021,22 +6029,22 @@
         <v>130</v>
       </c>
       <c r="U36" t="s">
+        <v>143</v>
+      </c>
+      <c r="W36" t="s">
         <v>144</v>
       </c>
-      <c r="W36" t="s">
-        <v>145</v>
-      </c>
       <c r="AB36" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC36" t="s">
         <v>150</v>
       </c>
-      <c r="AC36" t="s">
-        <v>151</v>
-      </c>
       <c r="AG36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -6077,28 +6085,28 @@
         <v>133</v>
       </c>
       <c r="O37" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="Q37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R37" t="s">
         <v>138</v>
       </c>
       <c r="U37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AB37" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AC37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AG37" t="s">
         <v>152</v>
       </c>
-      <c r="AG37" t="s">
-        <v>153</v>
-      </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -6130,7 +6138,7 @@
         <v>138</v>
       </c>
       <c r="K38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s">
         <v>133</v>
@@ -6139,25 +6147,25 @@
         <v>138</v>
       </c>
       <c r="O38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Q38" t="s">
         <v>136</v>
       </c>
       <c r="R38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -6186,31 +6194,31 @@
         <v>136</v>
       </c>
       <c r="K39" t="s">
+        <v>144</v>
+      </c>
+      <c r="L39" t="s">
+        <v>139</v>
+      </c>
+      <c r="N39" t="s">
+        <v>139</v>
+      </c>
+      <c r="O39" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>144</v>
+      </c>
+      <c r="R39" t="s">
+        <v>140</v>
+      </c>
+      <c r="U39" t="s">
         <v>145</v>
       </c>
-      <c r="L39" t="s">
-        <v>140</v>
-      </c>
-      <c r="N39" t="s">
-        <v>140</v>
-      </c>
-      <c r="O39" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>145</v>
-      </c>
-      <c r="R39" t="s">
-        <v>139</v>
-      </c>
-      <c r="U39" t="s">
-        <v>146</v>
-      </c>
       <c r="AB39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -6236,25 +6244,22 @@
         <v>138</v>
       </c>
       <c r="K40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N40" t="s">
         <v>136</v>
       </c>
       <c r="O40" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="R40" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -6277,22 +6282,22 @@
         <v>109</v>
       </c>
       <c r="I41" t="s">
+        <v>139</v>
+      </c>
+      <c r="K41" t="s">
+        <v>142</v>
+      </c>
+      <c r="L41" t="s">
         <v>140</v>
       </c>
-      <c r="K41" t="s">
-        <v>143</v>
-      </c>
-      <c r="L41" t="s">
-        <v>141</v>
-      </c>
       <c r="O41" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="R41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -6318,19 +6323,19 @@
         <v>136</v>
       </c>
       <c r="K42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O42" t="s">
         <v>149</v>
       </c>
       <c r="R42" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -6353,22 +6358,22 @@
         <v>138</v>
       </c>
       <c r="I43" t="s">
+        <v>144</v>
+      </c>
+      <c r="K43" t="s">
+        <v>147</v>
+      </c>
+      <c r="L43" t="s">
         <v>145</v>
       </c>
-      <c r="K43" t="s">
-        <v>148</v>
-      </c>
-      <c r="L43" t="s">
-        <v>146</v>
-      </c>
       <c r="O43" t="s">
+        <v>153</v>
+      </c>
+      <c r="R43" t="s">
         <v>150</v>
       </c>
-      <c r="R43" t="s">
-        <v>156</v>
-      </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -6388,22 +6393,22 @@
         <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I44" t="s">
+        <v>146</v>
+      </c>
+      <c r="L44" t="s">
         <v>147</v>
       </c>
-      <c r="L44" t="s">
-        <v>148</v>
-      </c>
       <c r="O44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R44" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -6420,25 +6425,22 @@
         <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O45" t="s">
-        <v>157</v>
-      </c>
-      <c r="R45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -6452,25 +6454,22 @@
         <v>117</v>
       </c>
       <c r="E46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F46" t="s">
         <v>136</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>153</v>
-      </c>
-      <c r="O46" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -6484,22 +6483,22 @@
         <v>132</v>
       </c>
       <c r="E47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G47" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -6513,16 +6512,16 @@
         <v>109</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G48" t="s">
         <v>149</v>
       </c>
       <c r="I48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -6536,16 +6535,16 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G49" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -6559,13 +6558,13 @@
         <v>135</v>
       </c>
       <c r="E50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -6579,13 +6578,13 @@
         <v>133</v>
       </c>
       <c r="E51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>134</v>
       </c>
@@ -6598,11 +6597,8 @@
       <c r="D52" t="s">
         <v>138</v>
       </c>
-      <c r="G52" t="s">
-        <v>157</v>
-      </c>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>109</v>
       </c>
@@ -6613,10 +6609,10 @@
         <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>130</v>
       </c>
@@ -6627,10 +6623,10 @@
         <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>133</v>
       </c>
@@ -6641,12 +6637,12 @@
         <v>133</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -6655,128 +6651,111 @@
         <v>138</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>136</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C58" t="s">
         <v>136</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
         <v>147</v>
       </c>
-      <c r="B59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" t="s">
-        <v>145</v>
-      </c>
-      <c r="D59" t="s">
-        <v>148</v>
-      </c>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>149</v>
-      </c>
-      <c r="B60" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" t="s">
-        <v>143</v>
-      </c>
-      <c r="D60" t="s">
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" t="s">
-        <v>146</v>
-      </c>
-      <c r="D61" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C62" t="s">
-        <v>148</v>
-      </c>
-      <c r="D62" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C63" t="s">
-        <v>154</v>
-      </c>
-      <c r="D63" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C64" t="s">
-        <v>139</v>
-      </c>
-      <c r="D64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6833,14 +6812,14 @@
     <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:DA42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -6872,7 +6851,7 @@
     <col min="98" max="98" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -7132,64 +7111,64 @@
         <v>138</v>
       </c>
       <c r="CI3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CJ3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="CK3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="CL3" t="s">
         <v>136</v>
       </c>
       <c r="CM3" t="s">
+        <v>144</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>142</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CR3" t="s">
         <v>145</v>
       </c>
-      <c r="CN3" t="s">
-        <v>141</v>
-      </c>
-      <c r="CO3" t="s">
+      <c r="CS3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CT3" t="s">
         <v>147</v>
       </c>
-      <c r="CP3" t="s">
-        <v>143</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>149</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>146</v>
-      </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
+        <v>155</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>153</v>
+      </c>
+      <c r="CW3" t="s">
         <v>150</v>
       </c>
-      <c r="CT3" t="s">
-        <v>148</v>
-      </c>
-      <c r="CU3" t="s">
+      <c r="CX3" t="s">
+        <v>152</v>
+      </c>
+      <c r="CY3" t="s">
         <v>156</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CZ3" t="s">
+        <v>151</v>
+      </c>
+      <c r="DA3" t="s">
         <v>154</v>
       </c>
-      <c r="CW3" t="s">
-        <v>151</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>153</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>157</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>152</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>155</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -7212,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -7230,7 +7209,7 @@
         <v>9</v>
       </c>
       <c r="N4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O4" t="s">
         <v>16</v>
@@ -7251,7 +7230,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V4" t="s">
         <v>9</v>
@@ -7506,7 +7485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7823,7 +7802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8140,7 +8119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -8457,7 +8436,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8687,7 +8666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -8917,7 +8896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -9147,7 +9126,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -9377,7 +9356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -9412,7 +9391,7 @@
         <v>29</v>
       </c>
       <c r="T12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -9559,7 +9538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -9741,7 +9720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -9923,7 +9902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -10105,7 +10084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -10137,7 +10116,7 @@
         <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T16" t="s">
         <v>11</v>
@@ -10260,7 +10239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -10415,7 +10394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -10570,7 +10549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -10725,7 +10704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -10844,9 +10823,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -10963,7 +10942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -11082,7 +11061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -11201,7 +11180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -11284,7 +11263,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -11367,7 +11346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -11450,7 +11429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -11533,11 +11512,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11553,10 +11532,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:DA1898"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.28515625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -11639,7 +11618,7 @@
     <col min="99" max="99" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -11899,1178 +11878,1178 @@
         <v>138</v>
       </c>
       <c r="CI3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CJ3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="CK3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="CL3" t="s">
         <v>136</v>
       </c>
       <c r="CM3" t="s">
+        <v>144</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>142</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CR3" t="s">
         <v>145</v>
       </c>
-      <c r="CN3" t="s">
-        <v>141</v>
-      </c>
-      <c r="CO3" t="s">
+      <c r="CS3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CT3" t="s">
         <v>147</v>
       </c>
-      <c r="CP3" t="s">
-        <v>143</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>149</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>146</v>
-      </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
+        <v>155</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>153</v>
+      </c>
+      <c r="CW3" t="s">
         <v>150</v>
       </c>
-      <c r="CT3" t="s">
-        <v>148</v>
-      </c>
-      <c r="CU3" t="s">
+      <c r="CX3" t="s">
+        <v>152</v>
+      </c>
+      <c r="CY3" t="s">
         <v>156</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CZ3" t="s">
+        <v>151</v>
+      </c>
+      <c r="DA3" t="s">
         <v>154</v>
       </c>
-      <c r="CW3" t="s">
-        <v>151</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>153</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>157</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>152</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>155</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" t="s">
         <v>159</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>160</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>161</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>162</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>163</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>164</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>165</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>166</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>167</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>168</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>169</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>170</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>171</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>172</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>173</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>175</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>176</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>177</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>178</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>179</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>180</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>181</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>182</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>183</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>184</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>185</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>186</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>187</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>188</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>189</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>190</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>191</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>192</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>193</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>194</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>195</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>196</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>197</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>198</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>199</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>200</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>201</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>202</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>203</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>204</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>205</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>206</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>207</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>208</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>209</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>210</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>211</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>212</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>213</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>214</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>215</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>216</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>217</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>218</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>219</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>220</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>221</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>222</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BN4" t="s">
         <v>223</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
         <v>224</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BP4" t="s">
         <v>225</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="BQ4" t="s">
         <v>226</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BR4" t="s">
         <v>227</v>
       </c>
-      <c r="BR4" t="s">
+      <c r="BS4" t="s">
         <v>228</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BT4" t="s">
         <v>229</v>
       </c>
-      <c r="BT4" t="s">
+      <c r="BU4" t="s">
         <v>230</v>
       </c>
-      <c r="BU4" t="s">
+      <c r="BV4" t="s">
         <v>231</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="BW4" t="s">
         <v>232</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>233</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="BY4" t="s">
         <v>234</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="BZ4" t="s">
         <v>235</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CA4" t="s">
         <v>236</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CB4" t="s">
         <v>237</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CC4" t="s">
         <v>238</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CD4" t="s">
         <v>239</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CE4" t="s">
         <v>240</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CF4" t="s">
         <v>241</v>
       </c>
-      <c r="CF4" t="s">
+      <c r="CG4" t="s">
         <v>242</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CH4" t="s">
         <v>243</v>
       </c>
-      <c r="CH4" t="s">
+      <c r="CI4" t="s">
         <v>244</v>
       </c>
-      <c r="CI4" t="s">
+      <c r="CJ4" t="s">
         <v>245</v>
       </c>
-      <c r="CJ4" t="s">
+      <c r="CK4" t="s">
         <v>246</v>
       </c>
-      <c r="CK4" t="s">
+      <c r="CL4" t="s">
         <v>247</v>
       </c>
-      <c r="CL4" t="s">
+      <c r="CM4" t="s">
         <v>248</v>
       </c>
-      <c r="CM4" t="s">
+      <c r="CN4" t="s">
         <v>249</v>
       </c>
-      <c r="CN4" t="s">
+      <c r="CO4" t="s">
         <v>250</v>
       </c>
-      <c r="CO4" t="s">
+      <c r="CP4" t="s">
         <v>251</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CQ4" t="s">
         <v>252</v>
       </c>
-      <c r="CQ4" t="s">
+      <c r="CR4" t="s">
         <v>253</v>
       </c>
-      <c r="CR4" t="s">
+      <c r="CS4" t="s">
         <v>254</v>
       </c>
-      <c r="CS4" t="s">
+      <c r="CT4" t="s">
         <v>255</v>
       </c>
-      <c r="CT4" t="s">
+      <c r="CU4" t="s">
         <v>256</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CV4" t="s">
         <v>257</v>
       </c>
-      <c r="CV4" t="s">
+      <c r="CW4" t="s">
         <v>258</v>
       </c>
-      <c r="CW4" t="s">
+      <c r="CX4" t="s">
         <v>259</v>
       </c>
-      <c r="CX4" t="s">
+      <c r="CY4" t="s">
         <v>260</v>
       </c>
-      <c r="CY4" t="s">
+      <c r="CZ4" t="s">
         <v>261</v>
       </c>
-      <c r="CZ4" t="s">
+      <c r="DA4" t="s">
         <v>262</v>
       </c>
-      <c r="DA4" t="s">
+    </row>
+    <row r="5" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>263</v>
       </c>
+      <c r="C5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J5" t="s">
+        <v>269</v>
+      </c>
+      <c r="K5" t="s">
+        <v>270</v>
+      </c>
+      <c r="L5" t="s">
+        <v>271</v>
+      </c>
+      <c r="M5" t="s">
+        <v>272</v>
+      </c>
+      <c r="O5" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>274</v>
+      </c>
+      <c r="R5" t="s">
+        <v>275</v>
+      </c>
+      <c r="T5" t="s">
+        <v>276</v>
+      </c>
+      <c r="V5" t="s">
+        <v>277</v>
+      </c>
+      <c r="W5" t="s">
+        <v>278</v>
+      </c>
+      <c r="X5" t="s">
+        <v>279</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>284</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>285</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>286</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>287</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>290</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>291</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>292</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>294</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>295</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>296</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>269</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>297</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>299</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>300</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>301</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>302</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>303</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>304</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>305</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>306</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>307</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>308</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>309</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>310</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>311</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>312</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>313</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>315</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>316</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>317</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>318</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>319</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>320</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>321</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>322</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>323</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>324</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>325</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>326</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>327</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>328</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>329</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>330</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>331</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>332</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>333</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>334</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>335</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G5" t="s">
-        <v>268</v>
-      </c>
-      <c r="H5" t="s">
-        <v>269</v>
-      </c>
-      <c r="J5" t="s">
-        <v>270</v>
-      </c>
-      <c r="K5" t="s">
-        <v>271</v>
-      </c>
-      <c r="L5" t="s">
-        <v>272</v>
-      </c>
-      <c r="M5" t="s">
-        <v>273</v>
-      </c>
-      <c r="O5" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>275</v>
-      </c>
-      <c r="R5" t="s">
-        <v>276</v>
-      </c>
-      <c r="T5" t="s">
-        <v>277</v>
-      </c>
-      <c r="V5" t="s">
-        <v>278</v>
-      </c>
-      <c r="W5" t="s">
-        <v>279</v>
-      </c>
-      <c r="X5" t="s">
-        <v>280</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>281</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>282</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>283</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>284</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>286</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>289</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>290</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>291</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>292</v>
-      </c>
-      <c r="AL5" t="s">
+    <row r="6" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H6" t="s">
+        <v>340</v>
+      </c>
+      <c r="J6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K6" t="s">
+        <v>342</v>
+      </c>
+      <c r="M6" t="s">
+        <v>343</v>
+      </c>
+      <c r="O6" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>345</v>
+      </c>
+      <c r="R6" t="s">
+        <v>346</v>
+      </c>
+      <c r="T6" t="s">
+        <v>347</v>
+      </c>
+      <c r="V6" t="s">
+        <v>348</v>
+      </c>
+      <c r="W6" t="s">
+        <v>349</v>
+      </c>
+      <c r="X6" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>352</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>353</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>355</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>356</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>357</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>358</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>359</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>362</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>363</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>366</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>368</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AW6" t="s">
         <v>293</v>
       </c>
-      <c r="AN5" t="s">
-        <v>294</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>294</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>295</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>296</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>294</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>297</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>270</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>299</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>300</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>301</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>302</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>303</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>304</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>305</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>306</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>307</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>308</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>309</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>310</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>311</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>312</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>313</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>314</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>315</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>316</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>317</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>318</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>319</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>320</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>321</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>322</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>323</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>324</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>325</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>326</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>327</v>
-      </c>
-      <c r="CJ5" t="s">
-        <v>328</v>
-      </c>
-      <c r="CL5" t="s">
-        <v>329</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>330</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>331</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>332</v>
-      </c>
-      <c r="CQ5" t="s">
-        <v>333</v>
-      </c>
-      <c r="CR5" t="s">
-        <v>334</v>
-      </c>
-      <c r="CS5" t="s">
-        <v>335</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>336</v>
+      <c r="AX6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>371</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>372</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>373</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>374</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>375</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>376</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>377</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>378</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>379</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>380</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>381</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>382</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>383</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>384</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>385</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>386</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>387</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>388</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>389</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>390</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>391</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>392</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>393</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>293</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>394</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>337</v>
-      </c>
-      <c r="C6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E6" t="s">
-        <v>339</v>
-      </c>
-      <c r="F6" t="s">
-        <v>340</v>
-      </c>
-      <c r="H6" t="s">
-        <v>341</v>
-      </c>
-      <c r="J6" t="s">
-        <v>342</v>
-      </c>
-      <c r="K6" t="s">
-        <v>343</v>
-      </c>
-      <c r="M6" t="s">
-        <v>344</v>
-      </c>
-      <c r="O6" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>346</v>
-      </c>
-      <c r="R6" t="s">
-        <v>347</v>
-      </c>
-      <c r="T6" t="s">
-        <v>348</v>
-      </c>
-      <c r="V6" t="s">
-        <v>349</v>
-      </c>
-      <c r="W6" t="s">
-        <v>350</v>
-      </c>
-      <c r="X6" t="s">
-        <v>351</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>352</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>353</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>354</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>355</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>357</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>358</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>359</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>360</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>361</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>362</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>363</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>364</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>365</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>366</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>367</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>368</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>369</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>370</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>294</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>371</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>372</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>373</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>374</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>375</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>376</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>377</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>378</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>379</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>380</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>381</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>382</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>383</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>384</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>385</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>386</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>388</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>389</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>390</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>391</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>392</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>393</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>394</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>294</v>
-      </c>
-      <c r="CN6" t="s">
+    <row r="7" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>395</v>
       </c>
+      <c r="C7" t="s">
+        <v>396</v>
+      </c>
+      <c r="E7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F7" t="s">
+        <v>398</v>
+      </c>
+      <c r="H7" t="s">
+        <v>399</v>
+      </c>
+      <c r="J7" t="s">
+        <v>400</v>
+      </c>
+      <c r="K7" t="s">
+        <v>401</v>
+      </c>
+      <c r="M7" t="s">
+        <v>402</v>
+      </c>
+      <c r="O7" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>404</v>
+      </c>
+      <c r="R7" t="s">
+        <v>405</v>
+      </c>
+      <c r="T7" t="s">
+        <v>406</v>
+      </c>
+      <c r="V7" t="s">
+        <v>407</v>
+      </c>
+      <c r="X7" t="s">
+        <v>408</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>409</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>411</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>413</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>414</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>415</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>416</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>417</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>418</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>419</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>420</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>421</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>422</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>423</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>424</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>425</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>426</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>427</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>428</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>429</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>430</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>431</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>432</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>433</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>434</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>435</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>436</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>437</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>438</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>439</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>440</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>441</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>442</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>443</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>444</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>445</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>446</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>396</v>
-      </c>
-      <c r="C7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E7" t="s">
-        <v>398</v>
-      </c>
-      <c r="F7" t="s">
-        <v>399</v>
-      </c>
-      <c r="H7" t="s">
-        <v>400</v>
-      </c>
-      <c r="J7" t="s">
-        <v>401</v>
-      </c>
-      <c r="K7" t="s">
-        <v>402</v>
-      </c>
-      <c r="M7" t="s">
-        <v>403</v>
-      </c>
-      <c r="O7" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>405</v>
-      </c>
-      <c r="R7" t="s">
-        <v>406</v>
-      </c>
-      <c r="T7" t="s">
-        <v>407</v>
-      </c>
-      <c r="V7" t="s">
-        <v>408</v>
-      </c>
-      <c r="X7" t="s">
-        <v>409</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>410</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>412</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>413</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>414</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>415</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>417</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>418</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>419</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>420</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>421</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>422</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>423</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>424</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>425</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>426</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>427</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>428</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>429</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>430</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>431</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>432</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>433</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>434</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>435</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>436</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>437</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>438</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>439</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>440</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>441</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>442</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>443</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>444</v>
-      </c>
-      <c r="CG7" t="s">
-        <v>445</v>
-      </c>
-      <c r="CH7" t="s">
-        <v>446</v>
-      </c>
-      <c r="CM7" t="s">
+    <row r="8" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>447</v>
       </c>
+      <c r="C8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E8" t="s">
+        <v>449</v>
+      </c>
+      <c r="F8" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" t="s">
+        <v>451</v>
+      </c>
+      <c r="K8" t="s">
+        <v>452</v>
+      </c>
+      <c r="O8" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>454</v>
+      </c>
+      <c r="R8" t="s">
+        <v>455</v>
+      </c>
+      <c r="T8" t="s">
+        <v>456</v>
+      </c>
+      <c r="X8" t="s">
+        <v>457</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>458</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>459</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>293</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>460</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>461</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>462</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>463</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>464</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>465</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>466</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>467</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>293</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>468</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>469</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>470</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>471</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>472</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>473</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>474</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>475</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>476</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>477</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>478</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>479</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>480</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>481</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>482</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>483</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>484</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>485</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>486</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>448</v>
-      </c>
-      <c r="C8" t="s">
-        <v>449</v>
-      </c>
-      <c r="E8" t="s">
-        <v>450</v>
-      </c>
-      <c r="F8" t="s">
-        <v>451</v>
-      </c>
-      <c r="H8" t="s">
-        <v>452</v>
-      </c>
-      <c r="K8" t="s">
-        <v>453</v>
-      </c>
-      <c r="O8" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>455</v>
-      </c>
-      <c r="R8" t="s">
-        <v>456</v>
-      </c>
-      <c r="T8" t="s">
-        <v>457</v>
-      </c>
-      <c r="X8" t="s">
-        <v>458</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>459</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>460</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>294</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>461</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>462</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>463</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>464</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>465</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>466</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>467</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>468</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>294</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>469</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>471</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>472</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>473</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>474</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>475</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>476</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>477</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>478</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>479</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>480</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>481</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>482</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>483</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>484</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>485</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>486</v>
-      </c>
-      <c r="CC8" t="s">
+    <row r="9" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>487</v>
       </c>
+      <c r="E9" t="s">
+        <v>488</v>
+      </c>
+      <c r="F9" t="s">
+        <v>489</v>
+      </c>
+      <c r="H9" t="s">
+        <v>490</v>
+      </c>
+      <c r="O9" t="s">
+        <v>491</v>
+      </c>
+      <c r="T9" t="s">
+        <v>492</v>
+      </c>
+      <c r="X9" t="s">
+        <v>493</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>494</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>498</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>499</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>500</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>501</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>502</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>503</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>504</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>505</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>506</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>507</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>508</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>509</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>510</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>511</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>512</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>513</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>488</v>
-      </c>
-      <c r="E9" t="s">
-        <v>489</v>
-      </c>
-      <c r="F9" t="s">
-        <v>490</v>
-      </c>
-      <c r="H9" t="s">
-        <v>491</v>
-      </c>
-      <c r="O9" t="s">
-        <v>492</v>
-      </c>
-      <c r="T9" t="s">
-        <v>493</v>
-      </c>
-      <c r="X9" t="s">
-        <v>494</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>495</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>498</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>499</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>500</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>501</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>502</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>503</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>504</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>505</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>506</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>507</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>508</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>509</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>510</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>511</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>512</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>513</v>
-      </c>
-      <c r="CC9" t="s">
+    <row r="10" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AO10" t="s">
         <v>514</v>
       </c>
+      <c r="AW10" t="s">
+        <v>515</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="41:49" x14ac:dyDescent="0.25">
-      <c r="AO10" t="s">
-        <v>515</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:105" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14955,6 +14934,6 @@
     <row r="1898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>